--- a/Data/Sensitivity Project 2.0.xlsx
+++ b/Data/Sensitivity Project 2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\ADC_Kplc_bill_reduction\Solar-Optimization-for-Telecom-sites\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDFA7A2-66A8-4F5A-A5B0-5433663F4177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73113431-D734-430E-8D54-188B7B271202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{F96E6A22-03C9-402C-9638-F170A625685D}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$1000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$1:$E$65</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3700,48 +3700,48 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="64" spans="1:14" s="24" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="16">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A64" s="4">
         <v>16</v>
       </c>
-      <c r="B64" s="17" t="s">
+      <c r="B64" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="C64" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D64" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="F64" s="19">
-        <v>18</v>
-      </c>
-      <c r="G64" s="20">
+      <c r="D64" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F64" s="7">
+        <v>18</v>
+      </c>
+      <c r="G64" s="8">
         <v>11.5</v>
       </c>
-      <c r="H64" s="21">
+      <c r="H64" s="9">
         <f t="shared" si="3"/>
         <v>51.75</v>
       </c>
-      <c r="I64" s="19"/>
-      <c r="J64" s="16">
+      <c r="I64" s="7"/>
+      <c r="J64" s="4">
         <v>800</v>
       </c>
-      <c r="K64" s="22">
+      <c r="K64" s="11">
         <f t="shared" si="4"/>
         <v>200</v>
       </c>
-      <c r="L64" s="21">
+      <c r="L64" s="15">
         <f t="shared" si="5"/>
         <v>43.6</v>
       </c>
-      <c r="M64" s="23">
+      <c r="M64" s="13">
         <v>89628</v>
       </c>
-      <c r="N64" s="23">
+      <c r="N64" s="13">
         <v>6.38</v>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C1000" xr:uid="{6AA46084-F924-4537-8708-65308EBA345A}"/>
+  <autoFilter ref="E1:E65" xr:uid="{6AA46084-F924-4537-8708-65308EBA345A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M65">
     <sortCondition ref="B1:B65"/>
   </sortState>

--- a/Data/Sensitivity Project 2.0.xlsx
+++ b/Data/Sensitivity Project 2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\ADC_Kplc_bill_reduction\Solar-Optimization-for-Telecom-sites\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73113431-D734-430E-8D54-188B7B271202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7252E2E5-C0E7-4B91-B1DE-CDA11CBFA72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{F96E6A22-03C9-402C-9638-F170A625685D}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="86">
   <si>
     <t>No.</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>Revised Average Load</t>
+  </si>
+  <si>
+    <t>PV Rating</t>
   </si>
 </sst>
 </file>
@@ -847,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA46084-F924-4537-8708-65308EBA345A}">
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -863,10 +866,11 @@
     <col min="11" max="11" width="13.08984375" customWidth="1"/>
     <col min="12" max="12" width="14.26953125" customWidth="1"/>
     <col min="13" max="13" width="13.54296875" style="14" customWidth="1"/>
-    <col min="14" max="14" width="10" style="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" style="14" customWidth="1"/>
+    <col min="15" max="15" width="9.26953125" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -909,8 +913,11 @@
       <c r="N1" s="12" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O1" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>10</v>
       </c>
@@ -954,8 +961,11 @@
       <c r="N2" s="13">
         <v>5.23</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O2" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>29</v>
       </c>
@@ -999,8 +1009,11 @@
       <c r="N3" s="13">
         <v>4.09</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O3" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>36</v>
       </c>
@@ -1044,8 +1057,11 @@
       <c r="N4" s="13">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" s="24" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O4" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16">
         <v>57</v>
       </c>
@@ -1089,8 +1105,11 @@
       <c r="N5" s="23">
         <v>4.47</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O5" s="23">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -1134,8 +1153,11 @@
       <c r="N6" s="13">
         <v>10.52</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O6" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>19</v>
       </c>
@@ -1179,8 +1201,11 @@
       <c r="N7" s="13">
         <v>4.6900000000000004</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O7" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>11</v>
       </c>
@@ -1224,8 +1249,11 @@
       <c r="N8" s="13">
         <v>6.87</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O8" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>63</v>
       </c>
@@ -1269,8 +1297,11 @@
       <c r="N9" s="13">
         <v>6.05</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O9" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>25</v>
       </c>
@@ -1314,8 +1345,11 @@
       <c r="N10" s="13">
         <v>4.58</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O10" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>1</v>
       </c>
@@ -1359,8 +1393,11 @@
       <c r="N11" s="13">
         <v>13.24</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O11" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>48</v>
       </c>
@@ -1404,8 +1441,11 @@
       <c r="N12" s="13">
         <v>2.23</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O12" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>44</v>
       </c>
@@ -1449,8 +1489,11 @@
       <c r="N13" s="13">
         <v>3.54</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O13" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>41</v>
       </c>
@@ -1494,8 +1537,11 @@
       <c r="N14" s="13">
         <v>2.5099999999999998</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O14" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>39</v>
       </c>
@@ -1539,8 +1585,11 @@
       <c r="N15" s="13">
         <v>2.4500000000000002</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O15" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -1584,8 +1633,11 @@
       <c r="N16" s="13">
         <v>6.81</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O16" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -1629,8 +1681,11 @@
       <c r="N17" s="13">
         <v>7.09</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O17" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
         <v>47</v>
       </c>
@@ -1674,8 +1729,11 @@
       <c r="N18" s="13">
         <v>2.34</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O18" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>7</v>
       </c>
@@ -1719,8 +1777,11 @@
       <c r="N19" s="13">
         <v>8.94</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O19" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
         <v>28</v>
       </c>
@@ -1764,8 +1825,11 @@
       <c r="N20" s="13">
         <v>5.67</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O20" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>24</v>
       </c>
@@ -1809,8 +1873,11 @@
       <c r="N21" s="13">
         <v>5.01</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O21" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>8</v>
       </c>
@@ -1854,8 +1921,11 @@
       <c r="N22" s="13">
         <v>8.61</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O22" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>23</v>
       </c>
@@ -1899,8 +1969,11 @@
       <c r="N23" s="13">
         <v>4.47</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O23" s="13">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
         <v>34</v>
       </c>
@@ -1944,8 +2017,11 @@
       <c r="N24" s="13">
         <v>3.22</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" s="24" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O24" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="16">
         <v>58</v>
       </c>
@@ -1989,8 +2065,11 @@
       <c r="N25" s="23">
         <v>4.47</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O25" s="23">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>5</v>
       </c>
@@ -2034,8 +2113,11 @@
       <c r="N26" s="13">
         <v>7.68</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O26" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>42</v>
       </c>
@@ -2079,8 +2161,11 @@
       <c r="N27" s="13">
         <v>2.29</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O27" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
         <v>13</v>
       </c>
@@ -2124,8 +2209,11 @@
       <c r="N28" s="13">
         <v>6.38</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O28" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>33</v>
       </c>
@@ -2169,8 +2257,11 @@
       <c r="N29" s="13">
         <v>2.67</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O29" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
         <v>26</v>
       </c>
@@ -2214,8 +2305,11 @@
       <c r="N30" s="13">
         <v>3.92</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O30" s="13">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>55</v>
       </c>
@@ -2259,8 +2353,11 @@
       <c r="N31" s="13">
         <v>7.63</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O31" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
         <v>4</v>
       </c>
@@ -2304,8 +2401,11 @@
       <c r="N32" s="13">
         <v>8.7200000000000006</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O32" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>18</v>
       </c>
@@ -2349,8 +2449,11 @@
       <c r="N33" s="13">
         <v>4.74</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" s="24" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O33" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="16">
         <v>53</v>
       </c>
@@ -2394,8 +2497,11 @@
       <c r="N34" s="23">
         <v>7.9</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" s="24" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O34" s="23">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="16">
         <v>62</v>
       </c>
@@ -2439,8 +2545,11 @@
       <c r="N35" s="23">
         <v>4.47</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O35" s="23">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
         <v>22</v>
       </c>
@@ -2484,8 +2593,11 @@
       <c r="N36" s="13">
         <v>4.3600000000000003</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O36" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
         <v>43</v>
       </c>
@@ -2529,8 +2641,11 @@
       <c r="N37" s="13">
         <v>2.02</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O37" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="4">
         <v>20</v>
       </c>
@@ -2574,8 +2689,11 @@
       <c r="N38" s="13">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O38" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>50</v>
       </c>
@@ -2619,8 +2737,11 @@
       <c r="N39" s="13">
         <v>2.23</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O39" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
         <v>56</v>
       </c>
@@ -2664,8 +2785,11 @@
       <c r="N40" s="13">
         <v>6.32</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O40" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>21</v>
       </c>
@@ -2709,8 +2833,11 @@
       <c r="N41" s="13">
         <v>4.8</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O41" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
         <v>40</v>
       </c>
@@ -2754,8 +2881,11 @@
       <c r="N42" s="13">
         <v>2.56</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O42" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
         <v>37</v>
       </c>
@@ -2799,8 +2929,11 @@
       <c r="N43" s="13">
         <v>2.78</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O43" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="4">
         <v>38</v>
       </c>
@@ -2844,8 +2977,11 @@
       <c r="N44" s="13">
         <v>2.29</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" s="24" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O44" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="16">
         <v>59</v>
       </c>
@@ -2889,8 +3025,11 @@
       <c r="N45" s="23">
         <v>3.38</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O45" s="23">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="4">
         <v>46</v>
       </c>
@@ -2934,8 +3073,11 @@
       <c r="N46" s="13">
         <v>2.4500000000000002</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O46" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
         <v>35</v>
       </c>
@@ -2979,8 +3121,11 @@
       <c r="N47" s="13">
         <v>2.78</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O47" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
         <v>27</v>
       </c>
@@ -3024,8 +3169,11 @@
       <c r="N48" s="13">
         <v>3.65</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O48" s="13">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>64</v>
       </c>
@@ -3069,8 +3217,11 @@
       <c r="N49" s="13">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" s="24" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O49" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="16">
         <v>61</v>
       </c>
@@ -3114,8 +3265,11 @@
       <c r="N50" s="23">
         <v>3.54</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O50" s="23">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
         <v>49</v>
       </c>
@@ -3159,8 +3313,11 @@
       <c r="N51" s="13">
         <v>2.02</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" s="24" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O51" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="16">
         <v>60</v>
       </c>
@@ -3204,8 +3361,11 @@
       <c r="N52" s="23">
         <v>4.58</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O52" s="23">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" s="4">
         <v>6</v>
       </c>
@@ -3249,8 +3409,11 @@
       <c r="N53" s="13">
         <v>8.1199999999999992</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O53" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" s="4">
         <v>2</v>
       </c>
@@ -3294,8 +3457,11 @@
       <c r="N54" s="13">
         <v>10.57</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" s="24" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O54" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="16">
         <v>52</v>
       </c>
@@ -3339,8 +3505,11 @@
       <c r="N55" s="23">
         <v>10.029999999999999</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O55" s="23">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="4">
         <v>30</v>
       </c>
@@ -3384,8 +3553,11 @@
       <c r="N56" s="13">
         <v>3.16</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O56" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="4">
         <v>9</v>
       </c>
@@ -3429,8 +3601,11 @@
       <c r="N57" s="13">
         <v>7.58</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O57" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="4">
         <v>51</v>
       </c>
@@ -3474,8 +3649,11 @@
       <c r="N58" s="13">
         <v>1.74</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O58" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="4">
         <v>54</v>
       </c>
@@ -3519,8 +3697,11 @@
       <c r="N59" s="13">
         <v>8.34</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O59" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="4">
         <v>31</v>
       </c>
@@ -3564,8 +3745,11 @@
       <c r="N60" s="13">
         <v>3.98</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O60" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="4">
         <v>45</v>
       </c>
@@ -3609,8 +3793,11 @@
       <c r="N61" s="13">
         <v>2.78</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O61" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="4">
         <v>12</v>
       </c>
@@ -3654,8 +3841,11 @@
       <c r="N62" s="13">
         <v>7.25</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O62" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="4">
         <v>17</v>
       </c>
@@ -3699,8 +3889,11 @@
       <c r="N63" s="13">
         <v>4.96</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O63" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="4">
         <v>16</v>
       </c>
@@ -3744,8 +3937,11 @@
       <c r="N64" s="13">
         <v>6.38</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O64" s="13">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
         <v>32</v>
       </c>
@@ -3788,6 +3984,9 @@
       </c>
       <c r="N65" s="13">
         <v>3.92</v>
+      </c>
+      <c r="O65" s="13">
+        <v>575</v>
       </c>
     </row>
   </sheetData>
